--- a/public/template/clothing_template.xlsx
+++ b/public/template/clothing_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\program\clothing-management-system\public\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7326A3F-2CDF-426F-9491-8F799C47FEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA6FE31-AC90-4B7B-82FC-C4E987596E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>例子</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -83,6 +83,22 @@
   </si>
   <si>
     <t>冬服</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尺码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>S,L,X,2X,3X,4X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缩略图</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -174,26 +190,26 @@
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -210,6 +226,111 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>158751</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>31408</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAC80B2B-6671-DBD7-6770-149F4649CED6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847851" y="812800"/>
+          <a:ext cx="158750" cy="209208"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>6301</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61C8FF11-F422-9B9A-321A-DC76F5660DBA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1847851" y="990600"/>
+          <a:ext cx="139699" cy="184101"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,30 +596,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="45" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.9140625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="12.08203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10.4140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.6640625" style="1"/>
+    <col min="1" max="1" width="12.33203125" style="2" customWidth="1"/>
+    <col min="2" max="4" width="11.9140625" style="2" customWidth="1"/>
+    <col min="5" max="7" width="12.08203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="12.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.4140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="8.6640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="50" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:11" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:8" ht="14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="14" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>3</v>
       </c>
@@ -506,76 +630,100 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+    <row r="3" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>1001</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2">
+      <c r="F3" s="4">
         <v>35</v>
       </c>
-      <c r="E3" s="6">
+      <c r="G3" s="4">
+        <v>65</v>
+      </c>
+      <c r="H3" s="6">
         <v>6</v>
       </c>
-      <c r="F3" s="2">
+      <c r="I3" s="4">
         <v>7</v>
       </c>
-      <c r="G3" s="2">
+      <c r="J3" s="4">
         <v>8</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="K3" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="14" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+    <row r="4" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>1002</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="2">
+      <c r="F4" s="4">
         <v>35</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="G4" s="4">
+        <v>55</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>